--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -26,8 +26,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 中奖档位
+2. 礼包档位</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>序列ID</t>
   </si>
@@ -35,9 +68,15 @@
     <t>中奖图标数量</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>#名称备注</t>
   </si>
   <si>
+    <t>礼包购买金额</t>
+  </si>
+  <si>
     <t>奖励1</t>
   </si>
   <si>
@@ -47,7 +86,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
@@ -56,6 +95,12 @@
     <t>name</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
     <t>getitem</t>
   </si>
   <si>
@@ -105,6 +150,30 @@
   </si>
   <si>
     <t>1990000_700000;1980000_40</t>
+  </si>
+  <si>
+    <t>礼包1</t>
+  </si>
+  <si>
+    <t>1022502_5</t>
+  </si>
+  <si>
+    <t>礼包2</t>
+  </si>
+  <si>
+    <t>1022502_10</t>
+  </si>
+  <si>
+    <t>礼包3</t>
+  </si>
+  <si>
+    <t>1022502_20</t>
+  </si>
+  <si>
+    <t>礼包4</t>
+  </si>
+  <si>
+    <t>1022502_50</t>
   </si>
 </sst>
 </file>
@@ -117,7 +186,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,8 +356,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,6 +378,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +706,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -638,16 +730,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -656,89 +748,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -754,7 +846,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1096,20 +1194,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1125,241 +1223,365 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
-      <c r="A5" s="1">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1">
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:5">
-      <c r="A6" s="1">
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="5">
+    <row r="7" spans="1:7">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="6">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="5">
+    <row r="8" spans="1:10">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="6">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="6">
         <v>1700</v>
       </c>
-      <c r="H8"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="5">
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="6">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="6">
         <v>1500</v>
       </c>
-      <c r="H9"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="5">
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="6">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="6">
         <v>1000</v>
       </c>
-      <c r="H10"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5">
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6">
         <v>500</v>
       </c>
-      <c r="H11"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="5">
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="6">
         <v>8</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="6">
         <v>200</v>
       </c>
-      <c r="H12"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="5">
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="6">
         <v>9</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="6">
         <v>100</v>
       </c>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="8:8">
-      <c r="H14"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="5"/>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="8:8">
-      <c r="H16"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18"/>
-    </row>
-    <row r="19" spans="8:8">
-      <c r="H19"/>
-    </row>
-    <row r="20" spans="8:8">
-      <c r="H20"/>
-    </row>
-    <row r="21" spans="8:8">
-      <c r="H21"/>
-    </row>
-    <row r="22" spans="8:8">
-      <c r="H22"/>
-    </row>
-    <row r="23" spans="8:8">
-      <c r="H23"/>
-    </row>
-    <row r="24" spans="8:8">
-      <c r="H24"/>
-    </row>
-    <row r="25" spans="8:8">
-      <c r="H25"/>
-    </row>
-    <row r="26" spans="8:8">
-      <c r="H26"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="7">
+        <v>101</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="7">
+        <v>199</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="7">
+        <v>102</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="7">
+        <v>999</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="7">
+        <v>103</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2999</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="7">
+        <v>104</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="10:10">
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="10:10">
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="10:10">
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="10:10">
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="10:10">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="10:10">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="10:10">
+      <c r="J24"/>
+    </row>
+    <row r="25" spans="10:10">
+      <c r="J25"/>
+    </row>
+    <row r="26" spans="10:10">
+      <c r="J26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9DCF8F-03FB-4FC2-9A94-75FDA52B1943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="1605" yWindow="300" windowWidth="15330" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -92,9 +98,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -174,19 +177,17 @@
   </si>
   <si>
     <t>1022502_50</t>
+  </si>
+  <si>
+    <t>iconNum</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,7 +197,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -213,150 +214,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -367,8 +224,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,204 +247,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -582,259 +272,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -843,7 +291,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -855,62 +303,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1188,14 +595,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
@@ -1207,7 +614,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1251,28 +658,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1281,7 +688,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1292,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1300,7 +707,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -1311,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1319,7 +726,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1330,17 +737,17 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="6">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -1351,18 +758,18 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6">
         <v>1700</v>
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -1373,18 +780,18 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="6">
         <v>1500</v>
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -1395,18 +802,18 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -1417,18 +824,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="6">
         <v>500</v>
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -1439,18 +846,18 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="6">
         <v>200</v>
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -1461,18 +868,18 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="6">
         <v>100</v>
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -1481,18 +888,18 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="7">
         <v>199</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="7"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -1501,18 +908,18 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="7">
         <v>999</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="7"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -1521,18 +928,18 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="7">
         <v>2999</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="7"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -1541,47 +948,47 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="7">
         <v>9999</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="7"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J18"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J19"/>
     </row>
-    <row r="20" spans="10:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J20"/>
     </row>
-    <row r="21" spans="10:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J21"/>
     </row>
-    <row r="22" spans="10:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J22"/>
     </row>
-    <row r="23" spans="10:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J23"/>
     </row>
-    <row r="24" spans="10:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J24"/>
     </row>
-    <row r="25" spans="10:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J25"/>
     </row>
-    <row r="26" spans="10:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J26"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9DCF8F-03FB-4FC2-9A94-75FDA52B1943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1605" yWindow="300" windowWidth="15330" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,6 +92,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>iconNum</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -177,17 +174,19 @@
   </si>
   <si>
     <t>1022502_50</t>
-  </si>
-  <si>
-    <t>iconNum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,7 +196,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -212,6 +211,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -224,21 +367,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,24 +377,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -272,17 +582,259 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -291,7 +843,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -303,21 +855,62 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -595,14 +1188,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
@@ -614,7 +1207,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -637,7 +1230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -658,28 +1251,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>37</v>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -688,7 +1281,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -699,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -707,7 +1300,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -718,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -726,7 +1319,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -737,17 +1330,17 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -758,18 +1351,18 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="6">
         <v>1700</v>
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -780,18 +1373,18 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="6">
         <v>1500</v>
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -802,18 +1395,18 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -824,18 +1417,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" s="6">
         <v>500</v>
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -846,18 +1439,18 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="6">
         <v>200</v>
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -868,18 +1461,18 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13" s="6">
         <v>100</v>
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -888,18 +1481,18 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="7">
         <v>199</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" s="7"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -908,18 +1501,18 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="7">
         <v>999</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="7"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -928,18 +1521,18 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="7">
         <v>2999</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="7"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -948,47 +1541,47 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="7">
         <v>9999</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" s="7"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:10">
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:10">
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="10:10">
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="10:10">
       <c r="J21"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="10:10">
       <c r="J22"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="10:10">
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="10:10">
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="10:10">
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="10:10">
       <c r="J26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -86,7 +86,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -113,43 +113,43 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_100000;1980000_10</t>
+    <t>1990000_20000</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_200000;1980000_15</t>
+    <t>1990000_80000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_300000;1980000_20</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_400000;1980000_25</t>
+    <t>1990000_120000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_500000;1980000_30</t>
+    <t>1990000_140000</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_600000;1980000_35</t>
+    <t>1990000_160000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_700000;1980000_40</t>
+    <t>1990000_180000</t>
   </si>
   <si>
     <t>礼包1</t>
@@ -1337,7 +1337,7 @@
         <v>17</v>
       </c>
       <c r="G7" s="6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1358,7 +1358,7 @@
         <v>19</v>
       </c>
       <c r="G8" s="6">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="J8"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="6">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J9"/>
     </row>
@@ -1424,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J11"/>
     </row>
@@ -1446,7 +1446,7 @@
         <v>27</v>
       </c>
       <c r="G12" s="6">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="J12"/>
     </row>
@@ -1468,7 +1468,7 @@
         <v>29</v>
       </c>
       <c r="G13" s="6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J13"/>
     </row>
@@ -1504,7 +1504,7 @@
         <v>32</v>
       </c>
       <c r="E15" s="7">
-        <v>999</v>
+        <v>399</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>33</v>
@@ -1524,7 +1524,7 @@
         <v>34</v>
       </c>
       <c r="E16" s="7">
-        <v>2999</v>
+        <v>799</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>35</v>
@@ -1544,7 +1544,7 @@
         <v>36</v>
       </c>
       <c r="E17" s="7">
-        <v>9999</v>
+        <v>1999</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>37</v>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A80B27-E643-4BD6-87BA-9D5C007AF010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -60,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>序列ID</t>
   </si>
@@ -174,19 +180,17 @@
   </si>
   <si>
     <t>1022502_50</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,7 +200,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -213,150 +217,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -367,8 +227,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,204 +250,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -582,259 +275,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -843,7 +294,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -855,62 +306,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1188,14 +598,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
@@ -1207,7 +617,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +651,8 @@
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
+      <c r="E2" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>8</v>
@@ -1251,7 +661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1272,7 +682,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1281,7 +691,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1300,7 +710,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -1319,7 +729,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1340,7 +750,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -1362,7 +772,7 @@
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -1384,7 +794,7 @@
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -1406,7 +816,7 @@
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -1428,7 +838,7 @@
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -1450,7 +860,7 @@
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -1472,7 +882,7 @@
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -1492,7 +902,7 @@
       <c r="G14" s="7"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -1512,7 +922,7 @@
       <c r="G15" s="7"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -1532,7 +942,7 @@
       <c r="G16" s="7"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -1552,36 +962,36 @@
       <c r="G17" s="7"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J18"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J19"/>
     </row>
-    <row r="20" spans="10:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J20"/>
     </row>
-    <row r="21" spans="10:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J21"/>
     </row>
-    <row r="22" spans="10:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J22"/>
     </row>
-    <row r="23" spans="10:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J23"/>
     </row>
-    <row r="24" spans="10:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J24"/>
     </row>
-    <row r="25" spans="10:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J25"/>
     </row>
-    <row r="26" spans="10:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J26"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A80B27-E643-4BD6-87BA-9D5C007AF010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,6 +86,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
@@ -180,17 +177,19 @@
   </si>
   <si>
     <t>1022502_50</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,7 +199,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -215,6 +214,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -227,21 +370,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,24 +380,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -275,17 +585,259 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -294,7 +846,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -306,21 +858,62 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -598,14 +1191,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
@@ -617,7 +1210,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -640,7 +1233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -651,38 +1244,38 @@
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="8" t="s">
-        <v>38</v>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -691,7 +1284,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -702,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -710,7 +1303,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -721,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -729,7 +1322,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -740,17 +1333,17 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -761,18 +1354,18 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="6">
         <v>1000</v>
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -783,18 +1376,18 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="6">
         <v>1000</v>
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -805,18 +1398,18 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -827,18 +1420,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="6">
         <v>1000</v>
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -849,18 +1442,18 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" s="6">
         <v>1000</v>
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -871,18 +1464,18 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="6">
         <v>1000</v>
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -891,18 +1484,18 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="7">
-        <v>199</v>
+        <v>0.99</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -911,18 +1504,18 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="7">
-        <v>399</v>
+        <v>2.99</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" s="7"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -931,18 +1524,18 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="7">
-        <v>799</v>
+        <v>9.99</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" s="7"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -951,47 +1544,47 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="7">
-        <v>1999</v>
+        <v>19.99</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" s="7"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:10">
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:10">
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="10:10">
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="10:10">
       <c r="J21"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="10:10">
       <c r="J22"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="10:10">
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="10:10">
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="10:10">
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="10:10">
       <c r="J26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>序列ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
@@ -1242,10 +1245,10 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>7</v>
@@ -1253,23 +1256,23 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1292,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1311,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1330,11 +1333,11 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="6">
         <v>1000</v>
@@ -1351,11 +1354,11 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="6">
         <v>1000</v>
@@ -1373,11 +1376,11 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="6">
         <v>1000</v>
@@ -1395,11 +1398,11 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
@@ -1417,11 +1420,11 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="6">
         <v>1000</v>
@@ -1439,11 +1442,11 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" s="6">
         <v>1000</v>
@@ -1461,11 +1464,11 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="6">
         <v>1000</v>
@@ -1481,13 +1484,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="7">
-        <v>199</v>
+        <v>0.99</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7"/>
       <c r="J14"/>
@@ -1501,13 +1504,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="7">
-        <v>399</v>
+        <v>2.99</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" s="7"/>
       <c r="J15"/>
@@ -1521,13 +1524,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="7">
-        <v>799</v>
+        <v>9.99</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" s="7"/>
       <c r="J16"/>
@@ -1541,13 +1544,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="7">
-        <v>1999</v>
+        <v>19.99</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" s="7"/>
       <c r="J17"/>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -116,49 +116,49 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_49500</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_80000</t>
+    <t>1990000_198000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_247500</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_120000</t>
+    <t>1990000_297000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_140000</t>
+    <t>1990000_346500</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_160000</t>
+    <t>1990000_396000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_180000</t>
+    <t>1990000_445500</t>
   </si>
   <si>
     <t>礼包1</t>
   </si>
   <si>
-    <t>1022502_5</t>
+    <t>1022502_1</t>
   </si>
   <si>
     <t>礼包2</t>
@@ -1507,7 +1507,7 @@
         <v>33</v>
       </c>
       <c r="E15" s="7">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
@@ -1527,7 +1527,7 @@
         <v>35</v>
       </c>
       <c r="E16" s="7">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>36</v>
@@ -1547,7 +1547,7 @@
         <v>37</v>
       </c>
       <c r="E17" s="7">
-        <v>19.99</v>
+        <v>49.99</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>38</v>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78B5B1C-C475-45DD-864B-77DEE2877431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -60,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>序列ID</t>
   </si>
@@ -177,19 +183,25 @@
   </si>
   <si>
     <t>1022502_50</t>
+  </si>
+  <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
+    <t>1_1|2_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -216,150 +228,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -370,8 +238,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,204 +254,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -585,251 +279,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -837,7 +289,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -846,7 +298,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -859,61 +311,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1191,26 +599,27 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
     <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
+    <col min="8" max="8" width="21.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
     <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1232,8 +641,11 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1253,8 +665,11 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -1274,8 +689,11 @@
       <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1284,7 +702,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1303,7 +721,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -1322,7 +740,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1343,7 +761,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -1365,7 +783,7 @@
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -1387,7 +805,7 @@
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -1409,7 +827,7 @@
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -1431,7 +849,7 @@
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -1453,7 +871,7 @@
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -1475,7 +893,7 @@
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -1493,9 +911,12 @@
         <v>32</v>
       </c>
       <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -1513,9 +934,12 @@
         <v>34</v>
       </c>
       <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -1527,15 +951,18 @@
         <v>35</v>
       </c>
       <c r="E16" s="7">
-        <v>19.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -1553,38 +980,41 @@
         <v>38</v>
       </c>
       <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J17"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J18"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J19"/>
     </row>
-    <row r="20" spans="10:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J20"/>
     </row>
-    <row r="21" spans="10:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J21"/>
     </row>
-    <row r="22" spans="10:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J22"/>
     </row>
-    <row r="23" spans="10:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J23"/>
     </row>
-    <row r="24" spans="10:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J24"/>
     </row>
-    <row r="25" spans="10:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J25"/>
     </row>
-    <row r="26" spans="10:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J26"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -55,12 +55,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>序列ID</t>
   </si>
@@ -83,6 +107,9 @@
     <t>中奖权重值</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -92,6 +119,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -110,55 +140,61 @@
     <t>weight</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>不中奖,奖励列表中不显示</t>
   </si>
   <si>
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_49500</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_80000</t>
+    <t>1990000_198000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_247500</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_120000</t>
+    <t>1990000_297000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_140000</t>
+    <t>1990000_346500</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_160000</t>
+    <t>1990000_396000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_180000</t>
+    <t>1990000_445500</t>
   </si>
   <si>
     <t>礼包1</t>
   </si>
   <si>
-    <t>1022502_5</t>
+    <t>1022502_1</t>
+  </si>
+  <si>
+    <t>1_google99|2_ios99</t>
   </si>
   <si>
     <t>礼包2</t>
@@ -167,16 +203,25 @@
     <t>1022502_10</t>
   </si>
   <si>
+    <t>1_google999|2_ios999</t>
+  </si>
+  <si>
     <t>礼包3</t>
   </si>
   <si>
     <t>1022502_20</t>
   </si>
   <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
     <t>礼包4</t>
   </si>
   <si>
     <t>1022502_50</t>
+  </si>
+  <si>
+    <t>1_google4999|2_ios4999</t>
   </si>
 </sst>
 </file>
@@ -199,7 +244,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -371,7 +416,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,13 +431,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,12 +557,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -555,12 +594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -799,37 +832,37 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -837,7 +870,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -846,7 +879,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1205,12 +1238,13 @@
     <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
+    <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
     <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1232,47 +1266,56 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1295,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1314,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1333,11 +1376,11 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6">
         <v>1000</v>
@@ -1354,11 +1397,11 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6">
         <v>1000</v>
@@ -1376,11 +1419,11 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G9" s="6">
         <v>1000</v>
@@ -1398,11 +1441,11 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
@@ -1420,11 +1463,11 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G11" s="6">
         <v>1000</v>
@@ -1442,11 +1485,11 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G12" s="6">
         <v>1000</v>
@@ -1464,11 +1507,11 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13" s="6">
         <v>1000</v>
@@ -1484,15 +1527,18 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" s="7">
         <v>0.99</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10">
@@ -1504,15 +1550,18 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="7">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="J15"/>
     </row>
     <row r="16" spans="1:10">
@@ -1524,15 +1573,18 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E16" s="7">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10">
@@ -1544,15 +1596,18 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E17" s="7">
-        <v>19.99</v>
+        <v>49.99</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="J17"/>
     </row>
     <row r="18" spans="10:10">

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78B5B1C-C475-45DD-864B-77DEE2877431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,12 +55,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>序列ID</t>
   </si>
@@ -89,6 +107,9 @@
     <t>中奖权重值</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -98,6 +119,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -116,6 +140,9 @@
     <t>weight</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>不中奖,奖励列表中不显示</t>
   </si>
   <si>
@@ -167,41 +194,47 @@
     <t>1022502_1</t>
   </si>
   <si>
+    <t>1_google99|2_ios99</t>
+  </si>
+  <si>
     <t>礼包2</t>
   </si>
   <si>
     <t>1022502_10</t>
   </si>
   <si>
+    <t>1_google999|2_ios999</t>
+  </si>
+  <si>
     <t>礼包3</t>
   </si>
   <si>
     <t>1022502_20</t>
   </si>
   <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
     <t>礼包4</t>
   </si>
   <si>
     <t>1022502_50</t>
   </si>
   <si>
-    <t>渠道商品ID</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
-    <t>channelCommodity</t>
-  </si>
-  <si>
-    <t>1_1|2_2</t>
+    <t>1_google4999|2_ios4999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +259,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -238,14 +415,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,24 +425,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -279,9 +618,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -311,17 +892,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -599,27 +1224,27 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
     <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="9" style="2"/>
     <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -642,58 +1267,58 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -702,7 +1327,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -713,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -721,7 +1346,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -732,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -740,7 +1365,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -751,17 +1376,17 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="6">
         <v>4</v>
       </c>
@@ -772,18 +1397,18 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6">
         <v>1000</v>
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -794,18 +1419,18 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G9" s="6">
         <v>1000</v>
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="6">
         <v>6</v>
       </c>
@@ -816,18 +1441,18 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G10" s="6">
         <v>1000</v>
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -838,18 +1463,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G11" s="6">
         <v>1000</v>
       </c>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="6">
         <v>8</v>
       </c>
@@ -860,18 +1485,18 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G12" s="6">
         <v>1000</v>
       </c>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -882,18 +1507,18 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13" s="6">
         <v>1000</v>
       </c>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="7">
         <v>101</v>
       </c>
@@ -902,21 +1527,21 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" s="7">
         <v>0.99</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="7">
         <v>102</v>
       </c>
@@ -925,21 +1550,21 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="7">
         <v>9.99</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="7">
         <v>103</v>
       </c>
@@ -948,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E16" s="7">
-        <v>19.989999999999998</v>
+        <v>19.99</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
@@ -962,7 +1587,7 @@
       </c>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="7">
         <v>104</v>
       </c>
@@ -971,50 +1596,50 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E17" s="7">
         <v>49.99</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="10:10">
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:10">
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="10:10">
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="10:10">
       <c r="J21"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="10:10">
       <c r="J22"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="10:10">
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="10:10">
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="10:10">
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="10:10">
       <c r="J26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -149,43 +149,43 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_49500</t>
+    <t>1990000_346500</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_198000</t>
+    <t>1990000_1386000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_247500</t>
+    <t>1990000_1732500</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_297000</t>
+    <t>1990000_2079000</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_346500</t>
+    <t>1990000_2425500</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_396000</t>
+    <t>1990000_2772000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_445500</t>
+    <t>1990000_3118500</t>
   </si>
   <si>
     <t>礼包1</t>
@@ -1244,7 +1244,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1327,7 +1327,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+    <row r="6" s="1" customFormat="1" spans="1:10">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1610,31 +1610,31 @@
       </c>
       <c r="J17"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="1:10">
       <c r="J18"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="1:10">
       <c r="J19"/>
     </row>
-    <row r="20" spans="10:10">
+    <row r="20" spans="1:10">
       <c r="J20"/>
     </row>
-    <row r="21" spans="10:10">
+    <row r="21" spans="1:10">
       <c r="J21"/>
     </row>
-    <row r="22" spans="10:10">
+    <row r="22" spans="1:10">
       <c r="J22"/>
     </row>
-    <row r="23" spans="10:10">
+    <row r="23" spans="1:10">
       <c r="J23"/>
     </row>
-    <row r="24" spans="10:10">
+    <row r="24" spans="1:10">
       <c r="J24"/>
     </row>
-    <row r="25" spans="10:10">
+    <row r="25" spans="1:10">
       <c r="J25"/>
     </row>
-    <row r="26" spans="10:10">
+    <row r="26" spans="1:10">
       <c r="J26"/>
     </row>
   </sheetData>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -149,49 +149,49 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_346500</t>
+    <t>1990000_173250</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
+    <t>1990000_693000</t>
+  </si>
+  <si>
+    <t>档位3</t>
+  </si>
+  <si>
+    <t>1990000_866250</t>
+  </si>
+  <si>
+    <t>档位4</t>
+  </si>
+  <si>
+    <t>1990000_1039500</t>
+  </si>
+  <si>
+    <t>档位5</t>
+  </si>
+  <si>
+    <t>1990000_1212750</t>
+  </si>
+  <si>
+    <t>档位6</t>
+  </si>
+  <si>
     <t>1990000_1386000</t>
   </si>
   <si>
-    <t>档位3</t>
-  </si>
-  <si>
-    <t>1990000_1732500</t>
-  </si>
-  <si>
-    <t>档位4</t>
-  </si>
-  <si>
-    <t>1990000_2079000</t>
-  </si>
-  <si>
-    <t>档位5</t>
-  </si>
-  <si>
-    <t>1990000_2425500</t>
-  </si>
-  <si>
-    <t>档位6</t>
-  </si>
-  <si>
-    <t>1990000_2772000</t>
-  </si>
-  <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_3118500</t>
+    <t>1990000_1559250</t>
   </si>
   <si>
     <t>礼包1</t>
   </si>
   <si>
-    <t>1022502_1</t>
+    <t>1022502_2</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
@@ -200,7 +200,7 @@
     <t>礼包2</t>
   </si>
   <si>
-    <t>1022502_10</t>
+    <t>1022502_20</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -209,7 +209,7 @@
     <t>礼包3</t>
   </si>
   <si>
-    <t>1022502_20</t>
+    <t>1022502_40</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
@@ -218,7 +218,7 @@
     <t>礼包4</t>
   </si>
   <si>
-    <t>1022502_50</t>
+    <t>1022502_100</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>序列ID</t>
   </si>
@@ -98,6 +98,9 @@
     <t>#名称备注</t>
   </si>
   <si>
+    <t>兑换消耗</t>
+  </si>
+  <si>
     <t>礼包购买金额</t>
   </si>
   <si>
@@ -113,12 +116,12 @@
     <t>int</t>
   </si>
   <si>
+    <t>map&lt;int{_}long&gt;{|}</t>
+  </si>
+  <si>
     <t>BigDecimal</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
-  </si>
-  <si>
     <t>map&lt;int{_}String&gt;{|}</t>
   </si>
   <si>
@@ -131,10 +134,13 @@
     <t>type</t>
   </si>
   <si>
+    <t>costItem</t>
+  </si>
+  <si>
     <t>cost</t>
   </si>
   <si>
-    <t>getitem</t>
+    <t>getItem</t>
   </si>
   <si>
     <t>weight</t>
@@ -209,19 +215,19 @@
     <t>礼包3</t>
   </si>
   <si>
+    <t>1980000_102</t>
+  </si>
+  <si>
     <t>1022502_40</t>
   </si>
   <si>
-    <t>1_google1999|2_ios1999</t>
-  </si>
-  <si>
     <t>礼包4</t>
   </si>
   <si>
+    <t>1980000_103</t>
+  </si>
+  <si>
     <t>1022502_100</t>
-  </si>
-  <si>
-    <t>1_google4999|2_ios4999</t>
   </si>
 </sst>
 </file>
@@ -234,7 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +263,18 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -416,7 +434,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,7 +449,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,58 +766,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -799,74 +823,80 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -878,17 +908,35 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1230,21 +1278,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
-    <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="23.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1307,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1266,376 +1316,395 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="A5" s="5">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:11">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="8">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5">
+      <c r="D5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
-      <c r="A6" s="5">
+    <row r="6" s="1" customFormat="1" spans="1:11">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5">
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8">
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6">
+    <row r="7" spans="1:11">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="10">
         <v>3</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="10">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="D7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="6">
+    <row r="8" spans="1:11">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="10">
         <v>4</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="D8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="10">
         <v>1000</v>
       </c>
-      <c r="J8"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="6">
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="10">
         <v>5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
         <v>1</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="D9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="10">
         <v>1000</v>
       </c>
-      <c r="J9"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6">
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="10">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="10">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="10">
         <v>1</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="D10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="10">
         <v>1000</v>
       </c>
-      <c r="J10"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="6">
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="10">
         <v>7</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="D11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="10">
         <v>1000</v>
       </c>
-      <c r="J11"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="6">
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="10">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="10">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="D12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="10">
         <v>1000</v>
       </c>
-      <c r="J12"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="6">
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="10">
         <v>9</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="10">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="D13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="10">
         <v>1000</v>
       </c>
-      <c r="J13"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="7">
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="12">
         <v>101</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
         <v>2</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="D14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12">
         <v>0.99</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="7">
+      <c r="G14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="12">
         <v>102</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12">
         <v>2</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="7">
+      <c r="D15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12">
         <v>9.99</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="7">
+      <c r="G15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="12">
         <v>103</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12">
         <v>2</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="7">
-        <v>19.99</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7" t="s">
+      <c r="D16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J16"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="7">
+      <c r="E16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="12">
         <v>104</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12">
         <v>2</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="7">
-        <v>49.99</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7" t="s">
+      <c r="D17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J17"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="J18"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="J19"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="J24"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="J25"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="J26"/>
+      <c r="E17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="K17"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="K19"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="K26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>序列ID</t>
   </si>
@@ -98,9 +98,6 @@
     <t>#名称备注</t>
   </si>
   <si>
-    <t>兑换消耗</t>
-  </si>
-  <si>
     <t>礼包购买金额</t>
   </si>
   <si>
@@ -116,12 +113,12 @@
     <t>int</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
-    <t>BigDecimal</t>
-  </si>
-  <si>
     <t>map&lt;int{_}String&gt;{|}</t>
   </si>
   <si>
@@ -134,13 +131,10 @@
     <t>type</t>
   </si>
   <si>
-    <t>costItem</t>
-  </si>
-  <si>
     <t>cost</t>
   </si>
   <si>
-    <t>getItem</t>
+    <t>getitem</t>
   </si>
   <si>
     <t>weight</t>
@@ -215,19 +209,19 @@
     <t>礼包3</t>
   </si>
   <si>
-    <t>1980000_102</t>
-  </si>
-  <si>
     <t>1022502_40</t>
   </si>
   <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
     <t>礼包4</t>
   </si>
   <si>
-    <t>1980000_103</t>
-  </si>
-  <si>
     <t>1022502_100</t>
+  </si>
+  <si>
+    <t>1_google4999|2_ios4999</t>
   </si>
 </sst>
 </file>
@@ -240,7 +234,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,18 +257,6 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -434,7 +416,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,19 +431,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,52 +736,58 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,80 +799,74 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -908,35 +878,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1278,23 +1230,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="23.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1257,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1316,395 +1266,376 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:11">
-      <c r="A5" s="8">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:10">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="6">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
-      <c r="A6" s="8">
+      <c r="G7" s="6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6">
+        <v>4</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="6">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="6">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="7">
+        <v>101</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
+      <c r="D14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="7">
+        <v>102</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="10">
-        <v>4</v>
-      </c>
-      <c r="B8" s="10">
-        <v>4</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K9"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="10">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10">
-        <v>6</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K10"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="10">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10">
-        <v>7</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K11"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="10">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10">
-        <v>8</v>
-      </c>
-      <c r="C12" s="10">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K12"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="10">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10">
-        <v>9</v>
-      </c>
-      <c r="C13" s="10">
-        <v>1</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="10">
-        <v>1000</v>
-      </c>
-      <c r="K13"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="12">
-        <v>101</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="D15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="7">
+        <v>9.99</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="7">
+        <v>103</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7">
         <v>2</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12">
-        <v>0.99</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="12">
-        <v>102</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="D16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="7">
+        <v>19.99</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="7">
+        <v>104</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7">
         <v>2</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="12">
-        <v>9.99</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="12">
-        <v>103</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
-        <v>2</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="D17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12" t="s">
+      <c r="E17" s="7">
+        <v>49.99</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="K16"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="12">
-        <v>104</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="K17"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="K19"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="K20"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="K21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="K22"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="K23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="K24"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="K25"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="K26"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="J24"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="J25"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="J26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -209,13 +209,13 @@
     <t>1022502_20</t>
   </si>
   <si>
-    <t>1_google999|2_ios999</t>
+    <t>1_google9999|2_ios9999</t>
   </si>
   <si>
     <t>礼包3</t>
   </si>
   <si>
-    <t>1980000_102</t>
+    <t>1980000_88888</t>
   </si>
   <si>
     <t>1022502_40</t>
@@ -224,7 +224,7 @@
     <t>礼包4</t>
   </si>
   <si>
-    <t>1980000_103</t>
+    <t>1980000_188888666</t>
   </si>
   <si>
     <t>1022502_100</t>
@@ -240,7 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,18 +263,6 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -434,18 +422,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -766,137 +748,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -908,35 +890,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1307,7 +1277,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1334,13 +1304,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -1361,13 +1331,13 @@
         <v>15</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -1382,301 +1352,301 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:11">
-      <c r="A5" s="8">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8">
+      <c r="E5" s="6"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
         <v>1500</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:11">
-      <c r="A6" s="8">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8">
+      <c r="E6" s="6"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
         <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="10">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="10">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>4</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="7">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="7">
         <v>1000</v>
       </c>
       <c r="K8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="10">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>5</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="7">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <v>1000</v>
       </c>
       <c r="K9"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="10">
+      <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>6</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="7">
         <v>1000</v>
       </c>
       <c r="K10"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="10">
+      <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>7</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>1000</v>
       </c>
       <c r="K11"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="10">
+      <c r="A12" s="7">
         <v>8</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>8</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="7">
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="7">
         <v>1000</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="10">
+      <c r="A13" s="7">
         <v>9</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>9</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="7">
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>1000</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="12">
+      <c r="A14" s="9">
         <v>101</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9">
         <v>2</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="12">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>0.99</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="9"/>
+      <c r="I14" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="12">
+      <c r="A15" s="9">
         <v>102</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9">
         <v>2</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="12">
-        <v>9.99</v>
-      </c>
-      <c r="G15" s="12" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
+        <v>99.99</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="9"/>
+      <c r="I15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="12">
+      <c r="A16" s="9">
         <v>103</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9">
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="12">
+      <c r="A17" s="9">
         <v>104</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9">
         <v>2</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11">

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -155,43 +155,43 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_173250</t>
+    <t>1990000_14900</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_693000</t>
+    <t>1990000_23800</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_866250</t>
+    <t>1990000_35600</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_1039500</t>
+    <t>1990000_41600</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_1212750</t>
+    <t>1990000_53500</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_1386000</t>
+    <t>1990000_68300</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_1559250</t>
+    <t>1990000_89100</t>
   </si>
   <si>
     <t>礼包1</t>
@@ -200,7 +200,7 @@
     <t>1022502_2</t>
   </si>
   <si>
-    <t>1_google99|2_ios99</t>
+    <t>1_google199|2_ios199</t>
   </si>
   <si>
     <t>礼包2</t>
@@ -209,25 +209,25 @@
     <t>1022502_20</t>
   </si>
   <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
+    <t>礼包3</t>
+  </si>
+  <si>
+    <t>1022502_50</t>
+  </si>
+  <si>
+    <t>1_google4999|2_ios4999</t>
+  </si>
+  <si>
+    <t>礼包4</t>
+  </si>
+  <si>
+    <t>1022502_100</t>
+  </si>
+  <si>
     <t>1_google9999|2_ios9999</t>
-  </si>
-  <si>
-    <t>礼包3</t>
-  </si>
-  <si>
-    <t>1980000_88888</t>
-  </si>
-  <si>
-    <t>1022502_40</t>
-  </si>
-  <si>
-    <t>礼包4</t>
-  </si>
-  <si>
-    <t>1980000_188888666</t>
-  </si>
-  <si>
-    <t>1022502_100</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="9">
-        <v>0.99</v>
+        <v>1.99</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>37</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="9">
-        <v>99.99</v>
+        <v>19.99</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>40</v>
@@ -1616,15 +1616,17 @@
       <c r="D16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
+        <v>49.99</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9"/>
+      <c r="I16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11">
@@ -1638,15 +1640,17 @@
       <c r="D17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
+        <v>99.99</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11">

--- a/hall/resources/sample/ScratchCards.xlsx
+++ b/hall/resources/sample/ScratchCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -155,43 +155,43 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_14900</t>
+    <t>1990000_173250</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_23800</t>
+    <t>1990000_693000</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_35600</t>
+    <t>1990000_866250</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_41600</t>
+    <t>1990000_1039500</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_53500</t>
+    <t>1990000_1212750</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_68300</t>
+    <t>1990000_1386000</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_89100</t>
+    <t>1990000_1559250</t>
   </si>
   <si>
     <t>礼包1</t>
@@ -200,7 +200,7 @@
     <t>1022502_2</t>
   </si>
   <si>
-    <t>1_google199|2_ios199</t>
+    <t>1_google99|2_ios99</t>
   </si>
   <si>
     <t>礼包2</t>
@@ -209,25 +209,25 @@
     <t>1022502_20</t>
   </si>
   <si>
-    <t>1_google1999|2_ios1999</t>
+    <t>1_google9999|2_ios9999</t>
   </si>
   <si>
     <t>礼包3</t>
   </si>
   <si>
-    <t>1022502_50</t>
-  </si>
-  <si>
-    <t>1_google4999|2_ios4999</t>
+    <t>1980000_88888</t>
+  </si>
+  <si>
+    <t>1022502_40</t>
   </si>
   <si>
     <t>礼包4</t>
   </si>
   <si>
+    <t>1980000_188888666</t>
+  </si>
+  <si>
     <t>1022502_100</t>
-  </si>
-  <si>
-    <t>1_google9999|2_ios9999</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="9">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>37</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="9">
-        <v>19.99</v>
+        <v>99.99</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>40</v>
@@ -1616,17 +1616,15 @@
       <c r="D16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9">
-        <v>49.99</v>
-      </c>
+      <c r="E16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="9"/>
       <c r="G16" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16" s="9"/>
-      <c r="I16" s="9" t="s">
-        <v>44</v>
-      </c>
+      <c r="I16" s="9"/>
       <c r="K16"/>
     </row>
     <row r="17" spans="1:11">
@@ -1640,17 +1638,15 @@
       <c r="D17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9">
-        <v>99.99</v>
-      </c>
+      <c r="E17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="9"/>
       <c r="G17" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="I17" s="9"/>
       <c r="K17"/>
     </row>
     <row r="18" spans="1:11">
